--- a/Tables/Data/__tables__.xlsx
+++ b/Tables/Data/__tables__.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -122,6 +122,15 @@
   </si>
   <si>
     <t>GameAttrInitTable.xlsx</t>
+  </si>
+  <si>
+    <t>battle.GameEffectTable</t>
+  </si>
+  <si>
+    <t>GameEffectRow</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -742,6 +751,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1063,10 +1075,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
-    <col min="2" max="2" width="20.375" customWidth="1"/>
+    <col min="2" max="2" width="22.75" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
     <col min="4" max="4" width="32.375" customWidth="1"/>
     <col min="5" max="5" width="24.375" customWidth="1"/>
@@ -1177,6 +1189,22 @@
         <v>29</v>
       </c>
     </row>
+    <row r="5" spans="1:11">
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Tables/Data/__tables__.xlsx
+++ b/Tables/Data/__tables__.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\__Dev\GAIS\Tables\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__Dev\GAIS\Tables\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17655"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
   <si>
     <t>##var</t>
   </si>
@@ -130,7 +130,16 @@
     <t>GameEffectRow</t>
   </si>
   <si>
-    <t/>
+    <t>battle.GameRougeEffectTable</t>
+  </si>
+  <si>
+    <t>GameRougeEffectRow</t>
+  </si>
+  <si>
+    <t>battle.GameSkillTable</t>
+  </si>
+  <si>
+    <t>GameSkillRow</t>
   </si>
 </sst>
 </file>
@@ -751,9 +760,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1075,11 +1081,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
-    <col min="2" max="2" width="22.75" customWidth="1"/>
-    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="26.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="32.375" customWidth="1"/>
     <col min="5" max="5" width="24.375" customWidth="1"/>
     <col min="6" max="9" width="18" customWidth="1"/>
@@ -1200,9 +1206,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="D6" s="2" t="s">
+    <row r="6" customFormat="1" spans="1:11">
+      <c r="B6" t="s">
         <v>32</v>
+      </c>
+      <c r="C6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="1" spans="1:11">
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Tables/Data/__tables__.xlsx
+++ b/Tables/Data/__tables__.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -130,16 +130,25 @@
     <t>GameEffectRow</t>
   </si>
   <si>
+    <t>GAIS/GameEffect</t>
+  </si>
+  <si>
     <t>battle.GameRougeEffectTable</t>
   </si>
   <si>
     <t>GameRougeEffectRow</t>
   </si>
   <si>
+    <t>GAIS/GameRougeEffect</t>
+  </si>
+  <si>
     <t>battle.GameSkillTable</t>
   </si>
   <si>
     <t>GameSkillRow</t>
+  </si>
+  <si>
+    <t>GAIS/GameSkill</t>
   </si>
 </sst>
 </file>
@@ -1205,27 +1214,36 @@
       <c r="D5" t="b">
         <v>0</v>
       </c>
+      <c r="E5" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="6" customFormat="1" spans="1:11">
       <c r="B6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="b">
         <v>0</v>
+      </c>
+      <c r="E6" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="1" spans="1:11">
       <c r="B7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D7" t="b">
         <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/Tables/Data/__tables__.xlsx
+++ b/Tables/Data/__tables__.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\__Dev\GAIS\Tables\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\__Dev\GAIS\Tables\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="43">
   <si>
     <t>##var</t>
   </si>
@@ -115,40 +115,52 @@
     <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
   </si>
   <si>
+    <t>battle.GameEffectTable</t>
+  </si>
+  <si>
+    <t>GameEffectRow</t>
+  </si>
+  <si>
+    <t>GAIS/GameEffect</t>
+  </si>
+  <si>
+    <t>battle.GameRougeEffectTable</t>
+  </si>
+  <si>
+    <t>GameRougeEffectRow</t>
+  </si>
+  <si>
+    <t>GAIS/GameRougeEffect</t>
+  </si>
+  <si>
+    <t>battle.GameSkillTable</t>
+  </si>
+  <si>
+    <t>GameSkillRow</t>
+  </si>
+  <si>
+    <t>GAIS/GameSkill</t>
+  </si>
+  <si>
+    <t>battle.GlobalBattleTable</t>
+  </si>
+  <si>
+    <t>GlobalBattleRow</t>
+  </si>
+  <si>
+    <t>battle/GlobalBattle.xlsx</t>
+  </si>
+  <si>
+    <t>one</t>
+  </si>
+  <si>
     <t>battle.GameAttrInitTable</t>
   </si>
   <si>
     <t>GameAttrInitRow</t>
   </si>
   <si>
-    <t>GameAttrInitTable.xlsx</t>
-  </si>
-  <si>
-    <t>battle.GameEffectTable</t>
-  </si>
-  <si>
-    <t>GameEffectRow</t>
-  </si>
-  <si>
-    <t>GAIS/GameEffect</t>
-  </si>
-  <si>
-    <t>battle.GameRougeEffectTable</t>
-  </si>
-  <si>
-    <t>GameRougeEffectRow</t>
-  </si>
-  <si>
-    <t>GAIS/GameRougeEffect</t>
-  </si>
-  <si>
-    <t>battle.GameSkillTable</t>
-  </si>
-  <si>
-    <t>GameSkillRow</t>
-  </si>
-  <si>
-    <t>GAIS/GameSkill</t>
+    <t>battle/GameAttrInit.xlsx</t>
   </si>
 </sst>
 </file>
@@ -161,7 +173,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,9 +184,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -283,6 +300,13 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -634,141 +658,150 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1090,160 +1123,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="6"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="7"/>
   <cols>
-    <col min="2" max="2" width="26.4166666666667" customWidth="1"/>
-    <col min="3" max="3" width="20" customWidth="1"/>
-    <col min="4" max="4" width="32.375" customWidth="1"/>
-    <col min="5" max="5" width="24.375" customWidth="1"/>
-    <col min="6" max="9" width="18" customWidth="1"/>
+    <col min="1" max="1" width="9" style="2"/>
+    <col min="2" max="2" width="30.75" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="29.75" style="2" customWidth="1"/>
+    <col min="6" max="6" width="25.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="32.125" style="2" customWidth="1"/>
+    <col min="8" max="9" width="18" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:11">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="3" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:11">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:11">
+      <c r="B5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:11">
+      <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>29</v>
+      <c r="E7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="6" customFormat="1" spans="1:11">
-      <c r="B6" t="s">
-        <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" customFormat="1" spans="1:11">
-      <c r="B7" t="s">
-        <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" t="s">
-        <v>38</v>
+    <row r="8" spans="1:11">
+      <c r="B8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Tables/Data/__tables__.xlsx
+++ b/Tables/Data/__tables__.xlsx
@@ -154,13 +154,13 @@
     <t>one</t>
   </si>
   <si>
-    <t>battle.GameAttrInitTable</t>
-  </si>
-  <si>
-    <t>GameAttrInitRow</t>
-  </si>
-  <si>
-    <t>battle/GameAttrInit.xlsx</t>
+    <t>battle.EnityInitTable</t>
+  </si>
+  <si>
+    <t>EnityInitRow</t>
+  </si>
+  <si>
+    <t>battle/EnityInit.xlsx</t>
   </si>
 </sst>
 </file>
@@ -788,14 +788,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22" applyFont="1">
@@ -1138,165 +1132,165 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:11">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="1" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" spans="1:11">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D4" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1" spans="1:11">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D5" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1" spans="1:11">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D6" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>37</v>
       </c>
       <c r="D7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:11">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>41</v>
       </c>
       <c r="D8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>42</v>
       </c>
     </row>
